--- a/Screw Drivers/Endbericht/Unterlagen/Zeiterfassung_Feb2025_Aug2026_Simon.xlsx
+++ b/Screw Drivers/Endbericht/Unterlagen/Zeiterfassung_Feb2025_Aug2026_Simon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\ScrewDriversMFG\Screw Drivers\Endbericht\Unterlagen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF0DC11-D30D-48DC-8F39-3683B68F6931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D876D67-2BD8-4700-BF18-2A929E4D22F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38355" yWindow="3825" windowWidth="28125" windowHeight="24495" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52710" yWindow="2565" windowWidth="22050" windowHeight="24495" tabRatio="500" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übersicht" sheetId="1" r:id="rId1"/>
@@ -1221,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1232,17 +1232,17 @@
     <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1250,42 +1250,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>10</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>18</v>
       </c>
@@ -1343,8 +1343,12 @@
         <f>'Feb 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16">
+        <f t="shared" ref="J16:J19" si="0">D16/C16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
@@ -1365,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="11">
-        <f t="shared" ref="F17:F34" si="0">F16+E17</f>
+        <f t="shared" ref="F17:F34" si="1">F16+E17</f>
         <v>0</v>
       </c>
       <c r="G17" s="9">
@@ -1376,8 +1380,12 @@
         <f>'Mär 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
@@ -1398,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="9">
@@ -1409,8 +1417,12 @@
         <f>'Apr 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>21</v>
       </c>
@@ -1431,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="9">
@@ -1442,8 +1454,12 @@
         <f>'Mai 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>22</v>
       </c>
@@ -1464,7 +1480,7 @@
         <v>-16</v>
       </c>
       <c r="F20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-16</v>
       </c>
       <c r="G20" s="9">
@@ -1475,8 +1491,12 @@
         <f>'Jun 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J20">
+        <f>D20/C20</f>
+        <v>0.90476190476190477</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>23</v>
       </c>
@@ -1497,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-16</v>
       </c>
       <c r="G21" s="9">
@@ -1508,8 +1528,12 @@
         <f>'Jul 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J21">
+        <f t="shared" ref="J21:J34" si="2">D21/C21</f>
+        <v>0.91304347826086951</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>24</v>
       </c>
@@ -1530,7 +1554,7 @@
         <v>-4</v>
       </c>
       <c r="F22" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-20</v>
       </c>
       <c r="G22" s="9">
@@ -1541,8 +1565,12 @@
         <f>'Aug 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>0.88095238095238093</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>25</v>
       </c>
@@ -1563,7 +1591,7 @@
         <v>-17</v>
       </c>
       <c r="F23" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-37</v>
       </c>
       <c r="G23" s="9">
@@ -1574,8 +1602,12 @@
         <f>'Sep 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <f t="shared" si="2"/>
+        <v>0.40340909090909088</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>26</v>
       </c>
@@ -1596,7 +1628,7 @@
         <v>-6</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-43</v>
       </c>
       <c r="G24" s="9">
@@ -1607,8 +1639,12 @@
         <f>'Okt 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>0.35869565217391303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>27</v>
       </c>
@@ -1629,7 +1665,7 @@
         <v>-4</v>
       </c>
       <c r="F25" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-47</v>
       </c>
       <c r="G25" s="9">
@@ -1640,8 +1676,12 @@
         <f>'Nov 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <f t="shared" si="2"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>28</v>
       </c>
@@ -1662,7 +1702,7 @@
         <v>-6</v>
       </c>
       <c r="F26" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-53</v>
       </c>
       <c r="G26" s="9">
@@ -1673,8 +1713,12 @@
         <f>'Dez 2025'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J26">
+        <f t="shared" si="2"/>
+        <v>0.35869565217391303</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>29</v>
       </c>
@@ -1695,7 +1739,7 @@
         <v>-12</v>
       </c>
       <c r="F27" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-65</v>
       </c>
       <c r="G27" s="9">
@@ -1706,8 +1750,12 @@
         <f>'Jan 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <f t="shared" si="2"/>
+        <v>0.47727272727272729</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>30</v>
       </c>
@@ -1728,7 +1776,7 @@
         <v>-24</v>
       </c>
       <c r="F28" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-89</v>
       </c>
       <c r="G28" s="9">
@@ -1739,8 +1787,12 @@
         <f>'Feb 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>31</v>
       </c>
@@ -1761,7 +1813,7 @@
         <v>-45</v>
       </c>
       <c r="F29" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-134</v>
       </c>
       <c r="G29" s="9">
@@ -1772,8 +1824,12 @@
         <f>'Mär 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J29">
+        <f t="shared" si="2"/>
+        <v>0.69886363636363635</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>32</v>
       </c>
@@ -1794,7 +1850,7 @@
         <v>-22</v>
       </c>
       <c r="F30" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-156</v>
       </c>
       <c r="G30" s="9">
@@ -1805,8 +1861,12 @@
         <f>'Apr 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J30">
+        <f t="shared" si="2"/>
+        <v>0.78409090909090906</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>33</v>
       </c>
@@ -1827,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-156</v>
       </c>
       <c r="G31" s="9">
@@ -1838,8 +1898,12 @@
         <f>'Mai 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>34</v>
       </c>
@@ -1860,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-156</v>
       </c>
       <c r="G32" s="9">
@@ -1871,8 +1935,12 @@
         <f>'Jun 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>35</v>
       </c>
@@ -1893,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-156</v>
       </c>
       <c r="G33" s="9">
@@ -1904,8 +1972,12 @@
         <f>'Jul 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <f t="shared" si="2"/>
+        <v>0.95652173913043481</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>36</v>
       </c>
@@ -1926,7 +1998,7 @@
         <v>-4</v>
       </c>
       <c r="F34" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-160</v>
       </c>
       <c r="G34" s="9">
@@ -1937,8 +2009,12 @@
         <f>'Aug 2026'!$B$41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J34">
+        <f t="shared" si="2"/>
+        <v>0.88095238095238093</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>37</v>
       </c>
